--- a/社区评论需求汇总.xlsx
+++ b/社区评论需求汇总.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区评论需求汇总" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'社区评论需求汇总'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'社区评论需求汇总'!$A$1:$M$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,22 +438,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,50 +529,58 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>7.23.0 (2024Q3)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>评论区发图</t>
+          <t>社区-话题</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>支持用户在评论中发布图片，包含图片上传、预览、删除功能；后端评论存储结构扩展支持图片字段；适配iOS/Android双端</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2</v>
+          <t>社区话题功能：首页话题卡片、帖子来源标签、话题榜搜索、话题详情页（结构+内容+评论列表）、话题定制分享</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>周颖</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-55968</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>需兼容已有评论展示；图片需接入审核</t>
+          <t>延期至7/26开始开发，因UI确认和搜索需求变更</t>
         </is>
       </c>
     </row>
@@ -582,39 +590,43 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>8.0.0 (2024Q3)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>社区帖子推荐优化</t>
+          <t>社区个人主页改版&amp;IM即时通信</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>优化社区首页Feed流推荐算法，增加基于用户兴趣的个性化推荐；新增'推荐'Tab页，合并原有'关注'和'发现'</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>3</v>
+          <t>社区个人主页改版(IP属地/创作数/热门帖子标签/帖子搜索/转评赞历史) + IM即时通信(用户鉴权/在线状态/拉黑/举报/@功能/草稿箱/长文发帖/回复盖楼)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>周颖</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,10 +634,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-57198</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>涉及推荐策略调整，需A/B测试</t>
+          <t>v8.0.0重点需求，含IM SDK集成</t>
         </is>
       </c>
     </row>
@@ -635,48 +651,60 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>8.0.0 (2024Q3)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>帖子点赞动效优化</t>
+          <t>消息中心改版</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>优化帖子点赞按钮的交互动效，增加点赞动画、点赞数实时更新；大V点赞特殊标识</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
+          <t>消息中心全面改版：财经资讯改版、交易提醒、热门事件、互动消息（社区/产品回复）、订阅更新、消息未读数</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>李克林/卢浩</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>胡金鑫</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-57562</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>含互动消息（社区、产品回复）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -684,52 +712,48 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>8.0.0 (2024Q3)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>创作者中心V2</t>
+          <t>点击新闻和724评论头像进个人主页</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>创作者中心二期建设：新增数据看板（阅读量/互动量/粉丝增长趋势）、内容管理后台（批量编辑/定时发布）、收益提现模块</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>4</v>
-      </c>
+          <t>在新闻和724快讯的评论区域点击用户头像进入个人主页</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>李克林/卢浩</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>依赖社区数据中台V2接口</t>
-        </is>
-      </c>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-57198</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -737,47 +761,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>8.0.0 (2024Q3)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>帖子评论排序优化</t>
+          <t>社区公约</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>评论支持按热度/时间排序切换；热评默认置顶；评论楼中楼展开优化</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>社区公约功能展示</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>李克林/卢浩</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-57198</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -786,52 +810,48 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>8.1.0 (2024Q4)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Feed流性能优化</t>
+          <t>社区个人主页分享海报</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>优化社区首页Feed流滑动性能，实现虚拟列表、图片懒加载、预加载策略</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>社区个人主页支持生成分享海报</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟/王强</t>
+          <t>杨怀展/卢浩</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Harmony端需单独适配</t>
-        </is>
-      </c>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58643</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -839,50 +859,58 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9.8.0 (20260318)</t>
+          <t>8.1.1 (2024Q4)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>社区搜索V3</t>
+          <t>社区消息类型push</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>社区搜索三期：支持帖子全文搜索、搜索联想词、搜索结果按分类筛选（帖子/用户/话题）、热门搜索榜</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>3</v>
+          <t>社区消息类型推送通知</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>杨怀展/卢浩</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>胡金鑫</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-57897</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>依赖搜索引擎升级</t>
+          <t>因8.0需求变更，待重新评审</t>
         </is>
       </c>
     </row>
@@ -892,39 +920,43 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9.8.0 (20260318)</t>
+          <t>8.1.1 (2024Q4)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>互动消息中心</t>
+          <t>社区v8.1需求（个人主页搜索/取消点赞/回复评论数）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>统一的消息中心：整合点赞、评论、关注、@等通知类型；支持消息分组、一键已读、消息跳转至原文</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>3</v>
+          <t>个人主页搜索帖子、列表显示回复的评论数、取消点赞功能</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明/王强</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>周颖</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -932,10 +964,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58459</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>需与IM消息区分展示</t>
+          <t>需求拆分：搜索+评论数(1d)，取消点赞(1.5d)</t>
         </is>
       </c>
     </row>
@@ -945,50 +981,54 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9.10.0 (20260506)</t>
+          <t>8.2.0 (2024Q4)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>帖子详情页改版</t>
+          <t>社区-草稿箱</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>帖子详情页UI重构：新增大图模式、相关推荐模块、评论区沉浸式体验、作者信息卡片增强</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>3</v>
+          <t>社区发帖草稿箱功能</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58521</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>设计稿评审中</t>
+          <t>长文草稿箱需要H5配合</t>
         </is>
       </c>
     </row>
@@ -998,47 +1038,55 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9.10.0 (20260506)</t>
+          <t>8.2.0 (2024Q4)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>社区关注推荐优化</t>
+          <t>搜索用户、社区的优化</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>优化关注流推荐策略：新增'可能感兴趣的人'模块、好友关注动态提醒、创作者入驻引导</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2</v>
+          <t>用户搜索和社区搜索功能优化</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>胡金鑫</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58824</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1047,39 +1095,43 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>10.6.0 (20260708)</t>
+          <t>8.3.0 (2024Q4)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>社区首页Feed流改版</t>
+          <t>24年社区首页改版</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>社区首页全面改版：Feed流样式升级（双列/单列切换）、视频自动播放、话题聚合卡片、直播入口</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>4</v>
+          <t>社区首页全面改版：关注Feed支持新闻评论/大V观点、热门feed、推荐&amp;热门顶部热门股票列表、推送数据给推荐系统</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明/王强</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>周颖</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1087,10 +1139,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58822</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>v10.6重点需求；含UI大改版</t>
+          <t>页面结构1d+帖子1d+新闻1d+大V观点3d+热门2d+推荐1d</t>
         </is>
       </c>
     </row>
@@ -1100,55 +1156,1093 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>secret (20260708)</t>
+          <t>8.3.0 (2024Q4)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>互动消息增加跳H5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>互动消息支持跳转至H5页面</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>杨怀展/卢浩</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>胡金鑫</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-59006</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>8.3.0 (2024Q4)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>消息中心：点赞跳转优化</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>消息中心点赞消息的跳转体验优化</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>杨怀展/卢浩</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>胡金鑫</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-59373</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>8.4.0 (2024Q4)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>股吧帖子支持期货挂链</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>股吧帖子支持期货挂链功能</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>杨怀展/卢浩</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58476</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>8.4.0 (2024Q4)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>社区首页推荐feed曝光点击数据埋点增加recommend_info上报</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>社区首页推荐Feed流的曝光点击数据埋点增加recommend_info字段上报</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-59528</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>8.4.0 (2024Q4)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>股吧回复支持上传1张图片</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>股吧回复评论支持上传1张图片</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>杨怀展/卢浩</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-58454</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>8.5.0 (2024Q4)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>话题详情页分享帖子套用话题分享海报</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>话题详情页分享帖子时使用话题专属分享海报</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>王战胜</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>8.7.0 (2025.1)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>股吧评论列表页显示已公开自选图标icon</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>在股吧评论列表页显示用户已公开的自选股图标</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>可以上</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-60603</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>9.4.0 (20251203)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>评论区发图</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>支持用户在评论中发布图片，包含图片上传、预览、删除功能</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>张伟/李明</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>需兼容已有评论展示</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>9.4.0 (20251203)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>社区帖子推荐优化</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>优化社区首页Feed流推荐算法，新增'推荐'Tab页</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>李明/张伟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>需A/B测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>9.4.0 (20251203)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>帖子点赞动效优化</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>优化帖子点赞按钮的交互动效</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>9.6.0 (20260114)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>创作者中心V2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>创作者中心二期：数据看板、内容管理后台、收益提现模块</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>李明/张伟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>依赖社区数据中台V2接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>9.6.0 (20260114)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>帖子评论排序优化</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>评论支持按热度/时间排序切换；热评置顶；楼中楼优化</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>9.6.0 (20260114)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Feed流性能优化</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>社区首页Feed流虚拟列表、图片懒加载、预加载</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>李明/张伟/王强</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Harmony端适配</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>9.8.0 (20260318)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>社区搜索V3</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>帖子全文搜索、搜索联想词、分类筛选、热门搜索榜</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>李明/张伟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>依赖搜索引擎升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>9.8.0 (20260318)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>互动消息中心</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>统一消息中心：点赞/评论/关注/@通知，消息分组、一键已读、跳转原文</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>张伟/李明/王强</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>需与IM消息区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>9.10.0 (20260506)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>帖子详情页改版</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>帖子详情页UI重构：大图模式、相关推荐、评论区沉浸式、作者信息卡片</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>张伟/李明</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>设计稿评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>9.10.0 (20260506)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>社区关注推荐优化</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>关注流推荐优化：可能感兴趣的人、好友动态提醒、创作者入驻引导</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>李明</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (20260708)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>社区首页Feed流改版</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>社区首页全面改版：双列/单列切换、视频自动播放、话题聚合、直播入口</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>张伟/李明/王强</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>v10.6重点需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (20260708)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>评论系统升级</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>评论系统全面升级：支持表情回复、评论置顶/折叠（作者功能）、评论举报、敏感词过滤增强、评论审核后台</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>评论系统全面升级：表情回复、评论置顶/折叠、举报、敏感词过滤、审核后台</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>张伟/李明/王强</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>需配合审核中台；含后台管理</t>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>需配合审核中台</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/社区评论需求汇总.xlsx
+++ b/社区评论需求汇总.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区评论需求汇总" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'社区评论需求汇总'!$A$1:$M$31</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +28,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,7 +71,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -438,25 +439,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
@@ -523,7 +524,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -584,7 +585,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -645,7 +646,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -706,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -755,7 +756,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -804,7 +805,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -853,7 +854,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -914,7 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -975,7 +976,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1032,7 +1033,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1089,7 +1090,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1150,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1203,7 +1204,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1252,7 +1253,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1309,7 +1310,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1366,7 +1367,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1423,7 +1424,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1464,7 +1465,7 @@
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1521,728 +1522,1545 @@
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>8.8.0 (2025.2.26)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>评论区发图</t>
+          <t>【鸿蒙】单框架新闻正文页增加评论</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>支持用户在评论中发布图片，包含图片上传、预览、删除功能</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>鸿蒙单框架下新闻正文页面增加评论功能</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>张伟/李明</t>
-        </is>
-      </c>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-59244</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>需兼容已有评论展示</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>纯鸿蒙需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>8.10.0 (2025.3.26)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>社区帖子推荐优化</t>
+          <t>个股评论右上角互动消息入口变为消息中心入口</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>优化社区首页Feed流推荐算法，新增'推荐'Tab页</t>
+          <t>个股评论页面右上角的互动消息入口改为消息中心入口</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>杨怀展/卢浩</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>需A/B测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>胡金鑫</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-62209</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>9.4.0 (20251203)</t>
+          <t>8.10.0 (2025.3.26)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>帖子点赞动效优化</t>
+          <t>社区首页发帖</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>优化帖子点赞按钮的交互动效</t>
+          <t>社区首页支持发帖功能</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-62012</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>8.10.0 (2025.3.26)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>创作者中心V2</t>
+          <t>iOS表情键盘加发送按钮</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>创作者中心二期：数据看板、内容管理后台、收益提现模块</t>
+          <t>iOS端评论表情键盘增加发送按钮</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>杨怀展</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-62099</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>依赖社区数据中台V2接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>仅iOS需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>8.12.0 (2025.4.23)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>帖子评论排序优化</t>
+          <t>社区及个人主页增加大V直播</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>评论支持按热度/时间排序切换；热评置顶；楼中楼优化</t>
+          <t>社区首页和个人主页增加大V直播功能入口</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-62764</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>9.6.0 (20260114)</t>
+          <t>9.0.0 (2025.10.10)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Feed流性能优化</t>
+          <t>讨论吧支持聚合个股评论中的新闻评论</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>社区首页Feed流虚拟列表、图片懒加载、预加载</t>
+          <t>讨论吧功能支持聚合展示个股评论中的新闻评论</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟/王强</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>周颖</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Harmony端适配</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-66936</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>9.8.0 (20260318)</t>
+          <t>9.0.0 (2025.10.10)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>社区搜索V3</t>
+          <t>个股评论列表页发主贴改为全屏发帖</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>帖子全文搜索、搜索联想词、分类筛选、热门搜索榜</t>
+          <t>个股评论列表页发送主贴改为全屏发帖模式</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>李明/张伟</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>依赖搜索引擎升级</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-66847</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>9.8.0 (20260318)</t>
+          <t>9.2.0 (2025.11.5)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>互动消息中心</t>
+          <t>消息中心新闻评论：删除</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>统一消息中心：点赞/评论/关注/@通知，消息分组、一键已读、跳转原文</t>
+          <t>消息中心中新闻评论支持删除操作</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明/王强</t>
+          <t>王战胜/臧宝亮</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>需与IM消息区分</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-67729</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>9.10.0 (20260506)</t>
+          <t>9.3.0 (2025.11.19)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>帖子详情页改版</t>
+          <t>社区首页一级菜单改由接口控制</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>帖子详情页UI重构：大图模式、相关推荐、评论区沉浸式、作者信息卡片</t>
+          <t>社区首页一级菜单改为由后端接口动态控制</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明</t>
+          <t>王战胜/臧宝亮/尹立冬</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>设计稿评审中</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-68038</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>9.10.0 (20260506)</t>
+          <t>9.5.0 (2025.12.17)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>社区关注推荐优化</t>
+          <t>社区付费投票</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>关注流推荐优化：可能感兴趣的人、好友动态提醒、创作者入驻引导</t>
+          <t>社区支持付费投票功能</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>王战胜/臧宝亮/尹立冬</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-67477</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>10.6.0 (20260708)</t>
+          <t>9.5.0 (2025.12.17)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>社区首页Feed流改版</t>
+          <t>个人主页显徽章</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>社区首页全面改版：双列/单列切换、视频自动播放、话题聚合、直播入口</t>
+          <t>个人主页展示用户徽章/炫彩标识</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>张伟/李明/王强</t>
+          <t>王战胜/臧宝亮/尹立冬</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>v10.6重点需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-68310</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>10.6.0 (20260708)</t>
+          <t>9.5.0 (2025.12.17)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>评论系统升级</t>
+          <t>互动消息交互优化</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>评论系统全面升级：表情回复、评论置顶/折叠、举报、敏感词过滤、审核后台</t>
+          <t>互动消息交互体验优化</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-68681</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>9.10.0 (2026.3.11)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>基金详情页发评论编辑框默认带上当前基金</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>基金详情页评论编辑框默认带上当前基金名称</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>何庆钊/曹海宽/张廷栋</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>钱丽娟</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-70163</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>9.10.0 (2026.3.11)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>【鸿蒙】端内分享到社区增加挂链</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙端内分享到社区功能增加挂链</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-69632</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>纯鸿蒙需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>10.0.0 (2026.4.22)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>基金评论合并</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>基金相关评论合并展示</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>何庆钊/曹海宽/张廷栋</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>钱丽娟</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-70603</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>10.0.0 (2026.4.22)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>社区-搜索按钮</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>社区页面增加搜索按钮</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-70647</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>10.0.0 (2026.4.22)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>社区-吧内屏蔽发帖</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>社区贴吧内支持屏蔽发帖</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71640</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>10.1.0 (2026.5.12)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>社区及行情评论-语音消息</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>社区及行情评论区支持语音消息发送</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-70514</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>10.1.0 (2026.5.12)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>社区-语音消息进草稿箱</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>社区语音消息支持保存到草稿箱</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71252</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>10.1.0 (2026.5.12)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>社区-大V私享会</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>社区大V私享会功能</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71094</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>10.1.0 (2026.5.12)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>社区-评论送票</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>社区评论支持送票功能</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71647</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>10.2.0 (2026.5.26)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>社区-投票分享改为长图</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>社区投票分享改为生成长图分享</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71032</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>10.2.0 (2026.5.26)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>社区-财头账号同步视频</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>社区财经头条账号同步视频内容</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-71340</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>10.3.0 (2026.6.10)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>IM-私信超链接</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>IM私信支持超链接功能</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>郑英博</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-72535</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>10.3.0 (2026.6.10)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>IM群公告超链接</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>IM群公告支持超链接功能</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>郑英博</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-72709</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (2026.7.8)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>社区-新增优质创作者称号</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>社区新增优质创作者称号展示</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>郑英博</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-70212</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (2026.7.8)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>IM-群聊禁言功能</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>IM群聊支持禁言功能</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>张伟/李明/王强</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>需配合审核中台</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>郑英博</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-73115</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (2026.7.8)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>视频-去除评论点赞按钮右侧的汉字</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>视频页面去除评论点赞按钮右侧的汉字文字</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>王战胜/臧宝亮/尹立冬</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>郑英博</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-73237</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (2026.7.8)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>推荐Feed流引入用户关注内容</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>推荐Feed流中引入用户关注的内容</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>杨怀展/卢浩/李克林</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>周颖</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-73249</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙需完善左下角文字标识显示不全逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>10.6.0 (2026.7.8)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>【鸿蒙】个人帖子显示阅读数</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙个人主页帖子增加阅读数显示</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>秦英</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>http://jira.intra.sina.com.cn/browse/SINAFINANCE-73223</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>纯鸿蒙需求</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>